--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_diff.xlsx
@@ -1,205 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,52 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -332,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -399,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -575,2173 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>5.5273494550734208E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.11699703020209409</v>
+        <v>0.05527349476496971</v>
       </c>
       <c r="D2">
-        <v>0.13272378875004279</v>
+        <v>0.1169970606969751</v>
       </c>
       <c r="E2">
-        <v>0.1300749895247697</v>
+        <v>0.1327238210400834</v>
       </c>
       <c r="F2">
-        <v>0.1883708066053518</v>
+        <v>0.1300749708161135</v>
       </c>
       <c r="G2">
-        <v>0.26453852984634019</v>
+        <v>0.1883709110375078</v>
       </c>
       <c r="H2">
-        <v>0.25470509926722867</v>
+        <v>0.2645385678840786</v>
       </c>
       <c r="I2">
-        <v>0.2927526184168005</v>
+        <v>0.2547051086097655</v>
       </c>
       <c r="J2">
-        <v>0.37648122516372889</v>
+        <v>0.2927526290925178</v>
       </c>
       <c r="K2">
-        <v>0.37222252709756148</v>
+        <v>0.3764812292232354</v>
       </c>
       <c r="L2">
-        <v>0.40904284152108561</v>
+        <v>0.3722225417170332</v>
       </c>
       <c r="M2">
-        <v>0.44407892220993211</v>
+        <v>0.4090428563558541</v>
       </c>
       <c r="N2">
-        <v>0.43741960194427759</v>
+        <v>0.4440789447842038</v>
       </c>
       <c r="O2">
-        <v>0.41859501659976789</v>
+        <v>0.437419626964147</v>
       </c>
       <c r="P2">
-        <v>0.40633617487430468</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4185950165258807</v>
+      </c>
+      <c r="Q2">
+        <v>0.4063361853907553</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>5.8722899276375452E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.37310080799210421</v>
+        <v>0.05872290264676747</v>
       </c>
       <c r="D3">
-        <v>0.44404777802975709</v>
+        <v>0.3731010134378259</v>
       </c>
       <c r="E3">
-        <v>0.34177923843633368</v>
+        <v>0.4440477857348362</v>
       </c>
       <c r="F3">
-        <v>0.33046896000685838</v>
+        <v>0.3417792879853324</v>
       </c>
       <c r="G3">
-        <v>0.34796933603627461</v>
+        <v>0.3304689794123949</v>
       </c>
       <c r="H3">
-        <v>0.38530516015267408</v>
+        <v>0.3479694858355524</v>
       </c>
       <c r="I3">
-        <v>0.41100115827036549</v>
+        <v>0.3853053803473962</v>
       </c>
       <c r="J3">
-        <v>0.41054298913569609</v>
+        <v>0.4110011262857212</v>
       </c>
       <c r="K3">
-        <v>0.42104977162767149</v>
+        <v>0.4105429750525174</v>
       </c>
       <c r="L3">
-        <v>0.45363472094945417</v>
+        <v>0.4210497405134436</v>
       </c>
       <c r="M3">
-        <v>0.49657292737703379</v>
+        <v>0.4536346746610564</v>
       </c>
       <c r="N3">
-        <v>0.55329261888215997</v>
+        <v>0.4965728473195439</v>
       </c>
       <c r="O3">
-        <v>0.60846779209101742</v>
+        <v>0.5532924357853378</v>
       </c>
       <c r="P3">
-        <v>0.60449642399546155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.608467686549939</v>
+      </c>
+      <c r="Q3">
+        <v>0.6044956704573096</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>4.7458373040784027E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>7.3477954549826391E-2</v>
+        <v>0.04745837649115981</v>
       </c>
       <c r="D4">
-        <v>0.17114380046366551</v>
+        <v>0.07347796892129717</v>
       </c>
       <c r="E4">
-        <v>0.19520276951655299</v>
+        <v>0.1711437910084743</v>
       </c>
       <c r="F4">
-        <v>0.36136417662623288</v>
+        <v>0.1952028036913407</v>
       </c>
       <c r="G4">
-        <v>0.31511034762772522</v>
+        <v>0.3613641465515263</v>
       </c>
       <c r="H4">
-        <v>0.29854554458524901</v>
+        <v>0.3151103251272449</v>
       </c>
       <c r="I4">
-        <v>0.3662827473118811</v>
+        <v>0.2985455558337458</v>
       </c>
       <c r="J4">
-        <v>0.40404754181787839</v>
+        <v>0.3662827451280232</v>
       </c>
       <c r="K4">
-        <v>0.43856138488319768</v>
+        <v>0.4040475073384091</v>
       </c>
       <c r="L4">
-        <v>0.44596655585463441</v>
+        <v>0.4385614119397281</v>
       </c>
       <c r="M4">
-        <v>0.44666608089371662</v>
+        <v>0.4459665586254868</v>
       </c>
       <c r="N4">
-        <v>0.44649203342045168</v>
+        <v>0.446666077506757</v>
       </c>
       <c r="O4">
-        <v>0.46296182386461421</v>
+        <v>0.4464920365768881</v>
       </c>
       <c r="P4">
-        <v>0.49939485793758442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4629618313580535</v>
+      </c>
+      <c r="Q4">
+        <v>0.4993948726375077</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4.5620027108750107E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.1653716925063764</v>
+        <v>0.0456200343861076</v>
       </c>
       <c r="D5">
-        <v>0.20645670746670411</v>
+        <v>0.1653717364830509</v>
       </c>
       <c r="E5">
-        <v>0.44738099349115862</v>
+        <v>0.2064570814028905</v>
       </c>
       <c r="F5">
-        <v>0.32477411893704611</v>
+        <v>0.4473809671599644</v>
       </c>
       <c r="G5">
-        <v>0.38777277427532558</v>
+        <v>0.3247741195705832</v>
       </c>
       <c r="H5">
-        <v>0.38564779976073138</v>
+        <v>0.3877728034301179</v>
       </c>
       <c r="I5">
-        <v>0.38486879094738158</v>
+        <v>0.3856478145740397</v>
       </c>
       <c r="J5">
-        <v>0.34865721529382648</v>
+        <v>0.3848688778487421</v>
       </c>
       <c r="K5">
-        <v>0.35040418265424711</v>
+        <v>0.348657219263351</v>
       </c>
       <c r="L5">
-        <v>0.36141962262739669</v>
+        <v>0.3504041495240348</v>
       </c>
       <c r="M5">
-        <v>0.38067705771588822</v>
+        <v>0.3614195989888115</v>
       </c>
       <c r="N5">
-        <v>0.43204468338792412</v>
+        <v>0.3806770210807914</v>
       </c>
       <c r="O5">
-        <v>0.46367354216923679</v>
+        <v>0.4320446243872793</v>
       </c>
       <c r="P5">
-        <v>0.51187871392204998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4636734528954385</v>
+      </c>
+      <c r="Q5">
+        <v>0.5118785972725044</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>4.4588323447701382E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.18558805468668571</v>
+        <v>0.04458832550646717</v>
       </c>
       <c r="D6">
-        <v>0.19301664935590779</v>
+        <v>0.185588140180875</v>
       </c>
       <c r="E6">
-        <v>0.45039146828596899</v>
+        <v>0.1930169026097386</v>
       </c>
       <c r="F6">
-        <v>0.29903687268441809</v>
+        <v>0.4503913976306477</v>
       </c>
       <c r="G6">
-        <v>0.32869166416003331</v>
+        <v>0.2990362039518562</v>
       </c>
       <c r="H6">
-        <v>0.3311663385883048</v>
+        <v>0.328696826597982</v>
       </c>
       <c r="I6">
-        <v>0.28040293017795392</v>
+        <v>0.3311665470340619</v>
       </c>
       <c r="J6">
-        <v>0.2852229343484996</v>
+        <v>0.2804029381483598</v>
       </c>
       <c r="K6">
-        <v>0.29969203879129569</v>
+        <v>0.2852231296157517</v>
       </c>
       <c r="L6">
-        <v>0.32087366220576102</v>
+        <v>0.2996921520825389</v>
       </c>
       <c r="M6">
-        <v>0.33968803066751702</v>
+        <v>0.320873683177118</v>
       </c>
       <c r="N6">
-        <v>0.37300441934802758</v>
+        <v>0.3396880478514363</v>
       </c>
       <c r="O6">
-        <v>0.38383100058182629</v>
+        <v>0.3730044247464891</v>
       </c>
       <c r="P6">
-        <v>0.43121112349880097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3838310003355084</v>
+      </c>
+      <c r="Q6">
+        <v>0.4312111572182677</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>4.8430520453452142E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>7.6222696096395121E-2</v>
+        <v>0.04843051886974707</v>
       </c>
       <c r="D7">
-        <v>0.1575904991744792</v>
+        <v>0.07622272717521578</v>
       </c>
       <c r="E7">
-        <v>0.1994063778723458</v>
+        <v>0.1575904718786855</v>
       </c>
       <c r="F7">
-        <v>0.32900173330767718</v>
+        <v>0.199406339391186</v>
       </c>
       <c r="G7">
-        <v>0.36862453900132502</v>
+        <v>0.3290017625106096</v>
       </c>
       <c r="H7">
-        <v>0.33909245358080498</v>
+        <v>0.3686244781927163</v>
       </c>
       <c r="I7">
-        <v>0.30017965073676961</v>
+        <v>0.3390924565976309</v>
       </c>
       <c r="J7">
-        <v>0.37037395702080822</v>
+        <v>0.3001795743627971</v>
       </c>
       <c r="K7">
-        <v>0.41444729235649258</v>
+        <v>0.3703738812958312</v>
       </c>
       <c r="L7">
-        <v>0.43662093085085257</v>
+        <v>0.4144472356040383</v>
       </c>
       <c r="M7">
-        <v>0.46102764350693171</v>
+        <v>0.4366209100710033</v>
       </c>
       <c r="N7">
-        <v>0.4212156969565542</v>
+        <v>0.4610276443522314</v>
       </c>
       <c r="O7">
-        <v>0.43356512622625393</v>
+        <v>0.4212163663744018</v>
       </c>
       <c r="P7">
-        <v>0.4549422286385274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4335651466376644</v>
+      </c>
+      <c r="Q7">
+        <v>0.4549422440643772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>4.575884647518233E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>7.9736681869914353E-2</v>
+        <v>0.04575884705913652</v>
       </c>
       <c r="D8">
-        <v>0.1786533514223145</v>
+        <v>0.07973669157480301</v>
       </c>
       <c r="E8">
-        <v>0.34287884531737062</v>
+        <v>0.1786534050198383</v>
       </c>
       <c r="F8">
-        <v>0.32786490989731137</v>
+        <v>0.3428788134042396</v>
       </c>
       <c r="G8">
-        <v>0.29712767939905199</v>
+        <v>0.3278648960013494</v>
       </c>
       <c r="H8">
-        <v>0.33356671527810999</v>
+        <v>0.2971277041918989</v>
       </c>
       <c r="I8">
-        <v>0.35131955414945443</v>
+        <v>0.3335667626063208</v>
       </c>
       <c r="J8">
-        <v>0.35635315727199679</v>
+        <v>0.3513195419765118</v>
       </c>
       <c r="K8">
-        <v>0.37760617782942468</v>
+        <v>0.3563531514340386</v>
       </c>
       <c r="L8">
-        <v>0.40035079358568221</v>
+        <v>0.3776061808581254</v>
       </c>
       <c r="M8">
-        <v>0.40092417498981409</v>
+        <v>0.4003508076119631</v>
       </c>
       <c r="N8">
-        <v>0.39605531953452611</v>
+        <v>0.4009241030677098</v>
       </c>
       <c r="O8">
-        <v>0.41284474291346063</v>
+        <v>0.3960552708112488</v>
       </c>
       <c r="P8">
-        <v>0.44263557280746191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4128447620648427</v>
+      </c>
+      <c r="Q8">
+        <v>0.4426355874985121</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>4.235133642966752E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>6.9258925326993584E-2</v>
+        <v>0.04235133680803167</v>
       </c>
       <c r="D9">
-        <v>0.16063182381914881</v>
+        <v>0.06925893899056994</v>
       </c>
       <c r="E9">
-        <v>0.29046209591590821</v>
+        <v>0.1606318822190954</v>
       </c>
       <c r="F9">
-        <v>0.2866851332329583</v>
+        <v>0.2904620625647979</v>
       </c>
       <c r="G9">
-        <v>0.24723291487233839</v>
+        <v>0.2866851382848676</v>
       </c>
       <c r="H9">
-        <v>0.27649141682059297</v>
+        <v>0.2472329183622222</v>
       </c>
       <c r="I9">
-        <v>0.27839814017885739</v>
+        <v>0.2764913623354402</v>
       </c>
       <c r="J9">
-        <v>0.28281061502745503</v>
+        <v>0.2783981160115521</v>
       </c>
       <c r="K9">
-        <v>0.28643583739681922</v>
+        <v>0.2828107482736751</v>
       </c>
       <c r="L9">
-        <v>0.32662150854415861</v>
+        <v>0.2864358504053611</v>
       </c>
       <c r="M9">
-        <v>0.29743245249426731</v>
+        <v>0.3266215244079469</v>
       </c>
       <c r="N9">
-        <v>0.3003448790068633</v>
+        <v>0.2974324656912923</v>
       </c>
       <c r="O9">
-        <v>0.31438728717025521</v>
+        <v>0.300344906045649</v>
       </c>
       <c r="P9">
-        <v>0.33525565260509033</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3143873173065469</v>
+      </c>
+      <c r="Q9">
+        <v>0.335255702168382</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>4.4845886958435978E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>7.9299623164726052E-2</v>
+        <v>0.04484588680889659</v>
       </c>
       <c r="D10">
-        <v>0.16855630040655439</v>
+        <v>0.07929967525613374</v>
       </c>
       <c r="E10">
-        <v>0.29281770834914211</v>
+        <v>0.1685563092013897</v>
       </c>
       <c r="F10">
-        <v>0.2872407265642784</v>
+        <v>0.2928176659970586</v>
       </c>
       <c r="G10">
-        <v>0.24527039786265839</v>
+        <v>0.2872407086248939</v>
       </c>
       <c r="H10">
-        <v>0.27223244136688529</v>
+        <v>0.2452704066478753</v>
       </c>
       <c r="I10">
-        <v>0.27337509257797249</v>
+        <v>0.2722323994039231</v>
       </c>
       <c r="J10">
-        <v>0.27151693445203068</v>
+        <v>0.2733750633550977</v>
       </c>
       <c r="K10">
-        <v>0.27652545204019169</v>
+        <v>0.2715168946859982</v>
       </c>
       <c r="L10">
-        <v>0.32141443397628378</v>
+        <v>0.2765254608087037</v>
       </c>
       <c r="M10">
-        <v>0.29152623762569252</v>
+        <v>0.3214145381112363</v>
       </c>
       <c r="N10">
-        <v>0.29348198062837427</v>
+        <v>0.2915263027620036</v>
       </c>
       <c r="O10">
-        <v>0.31394290497645999</v>
+        <v>0.29348201056825</v>
       </c>
       <c r="P10">
-        <v>0.33678664956727228</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3139429555314563</v>
+      </c>
+      <c r="Q10">
+        <v>0.3367867606941608</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>4.17565939156068E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>7.4607989883231196E-2</v>
+        <v>0.04175659582225402</v>
       </c>
       <c r="D11">
-        <v>0.16443678060174849</v>
+        <v>0.07460803854058098</v>
       </c>
       <c r="E11">
-        <v>0.2913979225460786</v>
+        <v>0.1644367828428424</v>
       </c>
       <c r="F11">
-        <v>0.28511040850676378</v>
+        <v>0.2913990199401048</v>
       </c>
       <c r="G11">
-        <v>0.2459225466870012</v>
+        <v>0.2851105701576814</v>
       </c>
       <c r="H11">
-        <v>0.28082860042638769</v>
+        <v>0.2459225517997243</v>
       </c>
       <c r="I11">
-        <v>0.28675404053673642</v>
+        <v>0.2808286208748152</v>
       </c>
       <c r="J11">
-        <v>0.29834247628636029</v>
+        <v>0.2867540434805684</v>
       </c>
       <c r="K11">
-        <v>0.29473992957109718</v>
+        <v>0.2983425114200812</v>
       </c>
       <c r="L11">
-        <v>0.32455316659682348</v>
+        <v>0.2947399251402097</v>
       </c>
       <c r="M11">
-        <v>0.30027780166632051</v>
+        <v>0.324553175310583</v>
       </c>
       <c r="N11">
-        <v>0.29537821649178481</v>
+        <v>0.3002778095086331</v>
       </c>
       <c r="O11">
-        <v>0.32096414112163008</v>
+        <v>0.2953782342855812</v>
       </c>
       <c r="P11">
-        <v>0.33275838287263432</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3209641788330635</v>
+      </c>
+      <c r="Q11">
+        <v>0.3327584539755619</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>4.0583119020438943E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.16030513228721679</v>
+        <v>0.04058312182212848</v>
       </c>
       <c r="D12">
-        <v>0.21276109103877419</v>
+        <v>0.1603051741610867</v>
       </c>
       <c r="E12">
-        <v>0.40872819541111632</v>
+        <v>0.2127615030383309</v>
       </c>
       <c r="F12">
-        <v>0.35305339603103442</v>
+        <v>0.4087281399153164</v>
       </c>
       <c r="G12">
-        <v>0.44177958508556298</v>
+        <v>0.3530534231172114</v>
       </c>
       <c r="H12">
-        <v>0.36133601804360638</v>
+        <v>0.4417796255953704</v>
       </c>
       <c r="I12">
-        <v>0.33566407686905719</v>
+        <v>0.3613360066889643</v>
       </c>
       <c r="J12">
-        <v>0.31425913090149521</v>
+        <v>0.3356641139144431</v>
       </c>
       <c r="K12">
-        <v>0.31519755550726009</v>
+        <v>0.31425911140297</v>
       </c>
       <c r="L12">
-        <v>0.33125719679070648</v>
+        <v>0.3151975362869684</v>
       </c>
       <c r="M12">
-        <v>0.34821036316023152</v>
+        <v>0.3312571720207675</v>
       </c>
       <c r="N12">
-        <v>0.39360423454022542</v>
+        <v>0.3482103277911247</v>
       </c>
       <c r="O12">
-        <v>0.43085850555921462</v>
+        <v>0.3936041877186149</v>
       </c>
       <c r="P12">
-        <v>0.50438832269644429</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4308584437358277</v>
+      </c>
+      <c r="Q12">
+        <v>0.5043882133310689</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>5.8215294348087747E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.29537534920858038</v>
+        <v>0.05821531768997379</v>
       </c>
       <c r="D13">
-        <v>0.29848599642016033</v>
+        <v>0.2953753753488533</v>
       </c>
       <c r="E13">
-        <v>0.45068269134521283</v>
+        <v>0.2984859962967251</v>
       </c>
       <c r="F13">
-        <v>0.4900011711353699</v>
+        <v>0.4506827715953484</v>
       </c>
       <c r="G13">
-        <v>0.46106158988518509</v>
+        <v>0.4900011760005933</v>
       </c>
       <c r="H13">
-        <v>0.54934017777774258</v>
+        <v>0.461061912370927</v>
       </c>
       <c r="I13">
-        <v>0.55600377201665718</v>
+        <v>0.5493323381317917</v>
       </c>
       <c r="J13">
-        <v>0.53670263269438101</v>
+        <v>0.5559854996073115</v>
       </c>
       <c r="K13">
-        <v>0.51111533912460549</v>
+        <v>0.5367033815606455</v>
       </c>
       <c r="L13">
-        <v>0.52094452811208658</v>
+        <v>0.5111152907872354</v>
       </c>
       <c r="M13">
-        <v>0.52226375068424924</v>
+        <v>0.5209445137668799</v>
       </c>
       <c r="N13">
-        <v>0.53415250740569842</v>
+        <v>0.5222637499984937</v>
       </c>
       <c r="O13">
-        <v>0.5365289614528419</v>
+        <v>0.5341524762175568</v>
       </c>
       <c r="P13">
-        <v>0.56738728488672674</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5365288957492695</v>
+      </c>
+      <c r="Q13">
+        <v>0.5673871631719029</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>5.0718071640209812E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>7.7389450019946682E-2</v>
+        <v>0.05071807334132933</v>
       </c>
       <c r="D14">
-        <v>0.15582012841936549</v>
+        <v>0.07738945000470022</v>
       </c>
       <c r="E14">
-        <v>0.18497952323531119</v>
+        <v>0.1558200137067716</v>
       </c>
       <c r="F14">
-        <v>0.299484129653034</v>
+        <v>0.1849796274930416</v>
       </c>
       <c r="G14">
-        <v>0.34360583350085472</v>
+        <v>0.2994843371310842</v>
       </c>
       <c r="H14">
-        <v>0.30163798571377942</v>
+        <v>0.343605756398204</v>
       </c>
       <c r="I14">
-        <v>0.25223949596768569</v>
+        <v>0.3016379971293829</v>
       </c>
       <c r="J14">
-        <v>0.30720082552548011</v>
+        <v>0.2522394795192631</v>
       </c>
       <c r="K14">
-        <v>0.35272910167742022</v>
+        <v>0.3072007960289427</v>
       </c>
       <c r="L14">
-        <v>0.35505801841344542</v>
+        <v>0.3527290790716155</v>
       </c>
       <c r="M14">
-        <v>0.34534664719516239</v>
+        <v>0.3550580617885865</v>
       </c>
       <c r="N14">
-        <v>0.32144518117458781</v>
+        <v>0.345346632173206</v>
       </c>
       <c r="O14">
-        <v>0.32955057395397291</v>
+        <v>0.3214451002471247</v>
       </c>
       <c r="P14">
-        <v>0.33626705881915459</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3295506026017813</v>
+      </c>
+      <c r="Q14">
+        <v>0.3362670927550364</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>5.2158215853461913E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>7.7335687775591064E-2</v>
+        <v>0.05215821585417852</v>
       </c>
       <c r="D15">
-        <v>0.15674430661808109</v>
+        <v>0.07733571965167452</v>
       </c>
       <c r="E15">
-        <v>0.19078222364556019</v>
+        <v>0.1567443193760161</v>
       </c>
       <c r="F15">
-        <v>0.30405952496710548</v>
+        <v>0.1907822092517892</v>
       </c>
       <c r="G15">
-        <v>0.33399835828965568</v>
+        <v>0.3040595116566405</v>
       </c>
       <c r="H15">
-        <v>0.29528747820913998</v>
+        <v>0.3339983137163292</v>
       </c>
       <c r="I15">
-        <v>0.25151277523621968</v>
+        <v>0.2952874736117039</v>
       </c>
       <c r="J15">
-        <v>0.31169809813854021</v>
+        <v>0.2515128139716813</v>
       </c>
       <c r="K15">
-        <v>0.35139075503756911</v>
+        <v>0.3116980808682129</v>
       </c>
       <c r="L15">
-        <v>0.35826617410454797</v>
+        <v>0.3513908123363656</v>
       </c>
       <c r="M15">
-        <v>0.36088596132255701</v>
+        <v>0.3582661345689283</v>
       </c>
       <c r="N15">
-        <v>0.33595271273526361</v>
+        <v>0.3608859713050988</v>
       </c>
       <c r="O15">
-        <v>0.3405732552659857</v>
+        <v>0.3359527289996153</v>
       </c>
       <c r="P15">
-        <v>0.34532946633856593</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3405732809809067</v>
+      </c>
+      <c r="Q15">
+        <v>0.345329496745522</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>4.5605043720765591E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>7.2702695997147002E-2</v>
+        <v>0.04560504514054883</v>
       </c>
       <c r="D16">
-        <v>0.15577410426201499</v>
+        <v>0.07270271720579505</v>
       </c>
       <c r="E16">
-        <v>0.1914322814335537</v>
+        <v>0.1557741024298521</v>
       </c>
       <c r="F16">
-        <v>0.3014987418747509</v>
+        <v>0.1914323199615061</v>
       </c>
       <c r="G16">
-        <v>0.34412275567039641</v>
+        <v>0.3014988821718952</v>
       </c>
       <c r="H16">
-        <v>0.30310616349256608</v>
+        <v>0.3441231051360296</v>
       </c>
       <c r="I16">
-        <v>0.26114890409545938</v>
+        <v>0.3031061447042889</v>
       </c>
       <c r="J16">
-        <v>0.3127815865194587</v>
+        <v>0.2611488837806561</v>
       </c>
       <c r="K16">
-        <v>0.3566276731356518</v>
+        <v>0.3127815836529283</v>
       </c>
       <c r="L16">
-        <v>0.36852338206801288</v>
+        <v>0.3566277676475235</v>
       </c>
       <c r="M16">
-        <v>0.3509501964549519</v>
+        <v>0.368523409557552</v>
       </c>
       <c r="N16">
-        <v>0.33352753068754909</v>
+        <v>0.3509502384739951</v>
       </c>
       <c r="O16">
-        <v>0.33819281794173051</v>
+        <v>0.3335275476542403</v>
       </c>
       <c r="P16">
-        <v>0.33515561541846511</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.3381928478362889</v>
+      </c>
+      <c r="Q16">
+        <v>0.3351556586435938</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>4.9663778034089057E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>7.801966949097365E-2</v>
+        <v>0.04966377780262816</v>
       </c>
       <c r="D17">
-        <v>0.15647445845928509</v>
+        <v>0.07801968077428083</v>
       </c>
       <c r="E17">
-        <v>0.18846523882794819</v>
+        <v>0.156474451496367</v>
       </c>
       <c r="F17">
-        <v>0.29931357213401821</v>
+        <v>0.1884652857189054</v>
       </c>
       <c r="G17">
-        <v>0.33542811679653622</v>
+        <v>0.2993136007787162</v>
       </c>
       <c r="H17">
-        <v>0.29723283204424139</v>
+        <v>0.3354283458280878</v>
       </c>
       <c r="I17">
-        <v>0.25525349335757658</v>
+        <v>0.2972328376703862</v>
       </c>
       <c r="J17">
-        <v>0.30839443412308809</v>
+        <v>0.2552536861337243</v>
       </c>
       <c r="K17">
-        <v>0.35098105766406729</v>
+        <v>0.3083944221376553</v>
       </c>
       <c r="L17">
-        <v>0.35788308261211388</v>
+        <v>0.3509810646321998</v>
       </c>
       <c r="M17">
-        <v>0.34863020266186961</v>
+        <v>0.3578833143177607</v>
       </c>
       <c r="N17">
-        <v>0.33958550022867412</v>
+        <v>0.3486302373457086</v>
       </c>
       <c r="O17">
-        <v>0.34988771183134543</v>
+        <v>0.3395855184223697</v>
       </c>
       <c r="P17">
-        <v>0.34639234779240508</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.3498877321897858</v>
+      </c>
+      <c r="Q17">
+        <v>0.3463923873632236</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>4.5693139847216541E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.16969609042046899</v>
+        <v>0.04569315180662301</v>
       </c>
       <c r="D18">
-        <v>0.22873487522078689</v>
+        <v>0.1696961303335817</v>
       </c>
       <c r="E18">
-        <v>0.43294644583507341</v>
+        <v>0.2287353157653852</v>
       </c>
       <c r="F18">
-        <v>0.34203294318949501</v>
+        <v>0.4329465877247857</v>
       </c>
       <c r="G18">
-        <v>0.40259015022091083</v>
+        <v>0.3420333728410238</v>
       </c>
       <c r="H18">
-        <v>0.45168258228285402</v>
+        <v>0.4025901864578667</v>
       </c>
       <c r="I18">
-        <v>0.38597025157837428</v>
+        <v>0.4516825786466283</v>
       </c>
       <c r="J18">
-        <v>0.32942267377365442</v>
+        <v>0.3859701872507359</v>
       </c>
       <c r="K18">
-        <v>0.32280465626898452</v>
+        <v>0.3294223038920821</v>
       </c>
       <c r="L18">
-        <v>0.34305811740688569</v>
+        <v>0.3228045511165855</v>
       </c>
       <c r="M18">
-        <v>0.36347698324841982</v>
+        <v>0.3430580924047916</v>
       </c>
       <c r="N18">
-        <v>0.41136865841956272</v>
+        <v>0.3634769503791524</v>
       </c>
       <c r="O18">
-        <v>0.46202027019036862</v>
+        <v>0.4113686054891935</v>
       </c>
       <c r="P18">
-        <v>0.49956667239011171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.462020174639128</v>
+      </c>
+      <c r="Q18">
+        <v>0.4995665468825821</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>4.6848510711796569E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.18859505981466751</v>
+        <v>0.04684852146645238</v>
       </c>
       <c r="D19">
-        <v>0.19142360242155379</v>
+        <v>0.1885951066677343</v>
       </c>
       <c r="E19">
-        <v>0.44482875769646613</v>
+        <v>0.1914237498976456</v>
       </c>
       <c r="F19">
-        <v>0.28261555751694828</v>
+        <v>0.4448286932867257</v>
       </c>
       <c r="G19">
-        <v>0.31947607667850669</v>
+        <v>0.2826155491646349</v>
       </c>
       <c r="H19">
-        <v>0.28949445528580747</v>
+        <v>0.3194761080507038</v>
       </c>
       <c r="I19">
-        <v>0.27415055333305632</v>
+        <v>0.2894944650617813</v>
       </c>
       <c r="J19">
-        <v>0.26452995016099812</v>
+        <v>0.2741505626541721</v>
       </c>
       <c r="K19">
-        <v>0.2791895547833641</v>
+        <v>0.2645299758017256</v>
       </c>
       <c r="L19">
-        <v>0.30254467290520748</v>
+        <v>0.2791895543628797</v>
       </c>
       <c r="M19">
-        <v>0.32875850920809419</v>
+        <v>0.302544677204965</v>
       </c>
       <c r="N19">
-        <v>0.37058720628247038</v>
+        <v>0.3287585150508641</v>
       </c>
       <c r="O19">
-        <v>0.38061838731672409</v>
+        <v>0.3705872109369303</v>
       </c>
       <c r="P19">
-        <v>0.41723026237465111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.3806183946748114</v>
+      </c>
+      <c r="Q19">
+        <v>0.4172302452575071</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.1132109440790127E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.2265634533829182</v>
+        <v>0.04113211744202241</v>
       </c>
       <c r="D20">
-        <v>0.22131563879171179</v>
+        <v>0.2265636385700701</v>
       </c>
       <c r="E20">
-        <v>0.25200551840374741</v>
+        <v>0.2213156817264079</v>
       </c>
       <c r="F20">
-        <v>0.24535401394621001</v>
+        <v>0.2520054403160853</v>
       </c>
       <c r="G20">
-        <v>0.31443776725889322</v>
+        <v>0.24535405013998</v>
       </c>
       <c r="H20">
-        <v>0.27440248975138742</v>
+        <v>0.314437823209334</v>
       </c>
       <c r="I20">
-        <v>0.26769446761477778</v>
+        <v>0.2744025081867756</v>
       </c>
       <c r="J20">
-        <v>0.25605946507929939</v>
+        <v>0.2676944586095064</v>
       </c>
       <c r="K20">
-        <v>0.27928814044107542</v>
+        <v>0.2560594708766385</v>
       </c>
       <c r="L20">
-        <v>0.31277504651515209</v>
+        <v>0.2792881459347118</v>
       </c>
       <c r="M20">
-        <v>0.34979366998400552</v>
+        <v>0.3127750787629743</v>
       </c>
       <c r="N20">
-        <v>0.32698922381726347</v>
+        <v>0.3497937084649978</v>
       </c>
       <c r="O20">
-        <v>0.35524310443471341</v>
+        <v>0.3269892384150176</v>
       </c>
       <c r="P20">
-        <v>0.37579171513727078</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3552430928318626</v>
+      </c>
+      <c r="Q20">
+        <v>0.3757916991325679</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>5.7979858445694289E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.34226982600440992</v>
+        <v>0.05797986117689032</v>
       </c>
       <c r="D21">
-        <v>0.41111742683491831</v>
+        <v>0.3422700206672701</v>
       </c>
       <c r="E21">
-        <v>0.32458608995284988</v>
+        <v>0.411117397652478</v>
       </c>
       <c r="F21">
-        <v>0.32310931375238627</v>
+        <v>0.3245861620113649</v>
       </c>
       <c r="G21">
-        <v>0.36604844425309851</v>
+        <v>0.3231093004741907</v>
       </c>
       <c r="H21">
-        <v>0.41822728446076612</v>
+        <v>0.3660484743272958</v>
       </c>
       <c r="I21">
-        <v>0.44819707510404277</v>
+        <v>0.4182272667501032</v>
       </c>
       <c r="J21">
-        <v>0.4244643423076217</v>
+        <v>0.4481970764230322</v>
       </c>
       <c r="K21">
-        <v>0.43544428508545457</v>
+        <v>0.4244643112255527</v>
       </c>
       <c r="L21">
-        <v>0.45251553751583812</v>
+        <v>0.4354442483058446</v>
       </c>
       <c r="M21">
-        <v>0.49831161000244228</v>
+        <v>0.4525154620481407</v>
       </c>
       <c r="N21">
-        <v>0.57270931713099327</v>
+        <v>0.4983114780767809</v>
       </c>
       <c r="O21">
-        <v>0.63212362556364277</v>
+        <v>0.5727091036253913</v>
       </c>
       <c r="P21">
-        <v>0.63632197089479081</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.6321232969437215</v>
+      </c>
+      <c r="Q21">
+        <v>0.636321584474931</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>5.339154393974746E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.32985551095834742</v>
+        <v>0.05339154776891965</v>
       </c>
       <c r="D22">
-        <v>0.39751800711880231</v>
+        <v>0.3298556988215746</v>
       </c>
       <c r="E22">
-        <v>0.31118910415516088</v>
+        <v>0.3975180070220174</v>
       </c>
       <c r="F22">
-        <v>0.31817814917215759</v>
+        <v>0.3111891174284761</v>
       </c>
       <c r="G22">
-        <v>0.35865454525138418</v>
+        <v>0.3181781464115284</v>
       </c>
       <c r="H22">
-        <v>0.43522851483757291</v>
+        <v>0.3586545297601074</v>
       </c>
       <c r="I22">
-        <v>0.48588104011829042</v>
+        <v>0.4352285685949986</v>
       </c>
       <c r="J22">
-        <v>0.46698672111986461</v>
+        <v>0.485880944919123</v>
       </c>
       <c r="K22">
-        <v>0.47845466467135039</v>
+        <v>0.4669866475607033</v>
       </c>
       <c r="L22">
-        <v>0.50956741701406982</v>
+        <v>0.4784545844482785</v>
       </c>
       <c r="M22">
-        <v>0.5340444720108144</v>
+        <v>0.509567335917728</v>
       </c>
       <c r="N22">
-        <v>0.58533147818327658</v>
+        <v>0.5340443162030559</v>
       </c>
       <c r="O22">
-        <v>0.60704062624832855</v>
+        <v>0.5853312149667194</v>
       </c>
       <c r="P22">
-        <v>0.62454864506259522</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.60704027991193</v>
+      </c>
+      <c r="Q22">
+        <v>0.6245482134409848</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>5.2725282777001697E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.268441555111601</v>
+        <v>0.05272529081715105</v>
       </c>
       <c r="D23">
-        <v>0.29271543226173602</v>
+        <v>0.2684414539279382</v>
       </c>
       <c r="E23">
-        <v>0.22225684153764891</v>
+        <v>0.2927154687994218</v>
       </c>
       <c r="F23">
-        <v>0.29859952246631682</v>
+        <v>0.2222568138120033</v>
       </c>
       <c r="G23">
-        <v>0.28832693353851208</v>
+        <v>0.2985995479146601</v>
       </c>
       <c r="H23">
-        <v>0.30487241515173669</v>
+        <v>0.2883269885326443</v>
       </c>
       <c r="I23">
-        <v>0.35298761619129537</v>
+        <v>0.3048724340913989</v>
       </c>
       <c r="J23">
-        <v>0.3697440882790789</v>
+        <v>0.3529876194436121</v>
       </c>
       <c r="K23">
-        <v>0.43136344495665718</v>
+        <v>0.3697440682257357</v>
       </c>
       <c r="L23">
-        <v>0.46980829562441762</v>
+        <v>0.4313632884280695</v>
       </c>
       <c r="M23">
-        <v>0.52998781761621494</v>
+        <v>0.4698080532120493</v>
       </c>
       <c r="N23">
-        <v>0.55065009797035913</v>
+        <v>0.5299874306982757</v>
       </c>
       <c r="O23">
-        <v>0.56746172128814054</v>
+        <v>0.5506496831227585</v>
       </c>
       <c r="P23">
-        <v>0.60564281871260839</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.5674612516550209</v>
+      </c>
+      <c r="Q23">
+        <v>0.6056423877410522</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>6.9446347666903455E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.12988701412066381</v>
+        <v>0.06944635710175849</v>
       </c>
       <c r="D24">
-        <v>0.2194777511801112</v>
+        <v>0.1298869471583537</v>
       </c>
       <c r="E24">
-        <v>0.2161036868243453</v>
+        <v>0.2194777692746535</v>
       </c>
       <c r="F24">
-        <v>0.2297761329879916</v>
+        <v>0.2161035240664112</v>
       </c>
       <c r="G24">
-        <v>0.21941810079128579</v>
+        <v>0.2297760266730364</v>
       </c>
       <c r="H24">
-        <v>0.30786748750374038</v>
+        <v>0.2194181004082362</v>
       </c>
       <c r="I24">
-        <v>0.44724604380842259</v>
+        <v>0.307867508545319</v>
       </c>
       <c r="J24">
-        <v>0.47072435083998337</v>
+        <v>0.447246071208654</v>
       </c>
       <c r="K24">
-        <v>0.46360169212938129</v>
+        <v>0.4707243454214402</v>
       </c>
       <c r="L24">
-        <v>0.47849326721974589</v>
+        <v>0.4636016787113855</v>
       </c>
       <c r="M24">
-        <v>0.57434865161094184</v>
+        <v>0.4784932239208197</v>
       </c>
       <c r="N24">
-        <v>0.68587994527939655</v>
+        <v>0.5743484764618315</v>
       </c>
       <c r="O24">
-        <v>0.76917506538698044</v>
+        <v>0.6858796464888124</v>
       </c>
       <c r="P24">
-        <v>0.87748519014092496</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.7691746883283805</v>
+      </c>
+      <c r="Q24">
+        <v>0.877484684382726</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>7.1882715704221375E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>0.13800514035031741</v>
+        <v>0.07188273636133972</v>
       </c>
       <c r="D25">
-        <v>0.24332826032536181</v>
+        <v>0.1380050820761219</v>
       </c>
       <c r="E25">
-        <v>0.23458663059346591</v>
+        <v>0.2433282780246703</v>
       </c>
       <c r="F25">
-        <v>0.2165112935498032</v>
+        <v>0.2345865732517572</v>
       </c>
       <c r="G25">
-        <v>0.2564458312591737</v>
+        <v>0.2165112282030814</v>
       </c>
       <c r="H25">
-        <v>0.5480425440695913</v>
+        <v>0.2564458404435794</v>
       </c>
       <c r="I25">
-        <v>0.52512516209659288</v>
+        <v>0.5480424708553595</v>
       </c>
       <c r="J25">
-        <v>0.51501797131892257</v>
+        <v>0.5251251104776135</v>
       </c>
       <c r="K25">
-        <v>0.49549068479470609</v>
+        <v>0.515017939394447</v>
       </c>
       <c r="L25">
-        <v>0.49950223655067222</v>
+        <v>0.4954906675674198</v>
       </c>
       <c r="M25">
-        <v>0.53714170089840252</v>
+        <v>0.4995022192831834</v>
       </c>
       <c r="N25">
-        <v>0.62019920742997847</v>
+        <v>0.5371416112694493</v>
       </c>
       <c r="O25">
-        <v>0.71330707705353424</v>
+        <v>0.6201990071833785</v>
       </c>
       <c r="P25">
-        <v>0.80655042011626887</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.7133067501147382</v>
+      </c>
+      <c r="Q25">
+        <v>0.8065500161847194</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>7.9347360529910552E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>0.1580148201164793</v>
+        <v>0.07934741865464547</v>
       </c>
       <c r="D26">
-        <v>0.20329686232075769</v>
+        <v>0.1580147707648958</v>
       </c>
       <c r="E26">
-        <v>0.19821039854216019</v>
+        <v>0.2032968756330936</v>
       </c>
       <c r="F26">
-        <v>0.26417975481023842</v>
+        <v>0.1982104221517844</v>
       </c>
       <c r="G26">
-        <v>0.26291079998942402</v>
+        <v>0.2641797297567102</v>
       </c>
       <c r="H26">
-        <v>0.37344082469500012</v>
+        <v>0.2629108227403513</v>
       </c>
       <c r="I26">
-        <v>0.60785735223695181</v>
+        <v>0.3734408275872235</v>
       </c>
       <c r="J26">
-        <v>0.50583840133820857</v>
+        <v>0.607857783465682</v>
       </c>
       <c r="K26">
-        <v>0.51124314930185899</v>
+        <v>0.5058382800477522</v>
       </c>
       <c r="L26">
-        <v>0.55070167358944899</v>
+        <v>0.5112431563906064</v>
       </c>
       <c r="M26">
-        <v>0.64101573112372801</v>
+        <v>0.5507016579135987</v>
       </c>
       <c r="N26">
-        <v>0.70760756237618738</v>
+        <v>0.6410155963674374</v>
       </c>
       <c r="O26">
-        <v>0.78929521505099276</v>
+        <v>0.7076073306786799</v>
       </c>
       <c r="P26">
-        <v>0.90253027547812492</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.7892948603503277</v>
+      </c>
+      <c r="Q26">
+        <v>0.9025298087285865</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>7.7020972979223293E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>0.13971193158635939</v>
+        <v>0.07702103245797456</v>
       </c>
       <c r="D27">
-        <v>0.18172741459534569</v>
+        <v>0.1397118827743401</v>
       </c>
       <c r="E27">
-        <v>0.1643012974579238</v>
+        <v>0.1817274483181517</v>
       </c>
       <c r="F27">
-        <v>0.21738782225893599</v>
+        <v>0.1643012617920322</v>
       </c>
       <c r="G27">
-        <v>0.2090293824360267</v>
+        <v>0.2173877839186381</v>
       </c>
       <c r="H27">
-        <v>0.2451302659389081</v>
+        <v>0.2090293949604985</v>
       </c>
       <c r="I27">
-        <v>0.42478475838944779</v>
+        <v>0.2451302638792269</v>
       </c>
       <c r="J27">
-        <v>0.35871576864014543</v>
+        <v>0.4247852181207813</v>
       </c>
       <c r="K27">
-        <v>0.34494447222475921</v>
+        <v>0.3587157942332306</v>
       </c>
       <c r="L27">
-        <v>0.3233185641548374</v>
+        <v>0.3449444597246841</v>
       </c>
       <c r="M27">
-        <v>0.38600450692706939</v>
+        <v>0.3233185452751863</v>
       </c>
       <c r="N27">
-        <v>0.38356062497861237</v>
+        <v>0.386004475334902</v>
       </c>
       <c r="O27">
-        <v>0.42615153957926538</v>
+        <v>0.3835606165113076</v>
       </c>
       <c r="P27">
-        <v>0.45416522356453559</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.4261514845237723</v>
+      </c>
+      <c r="Q27">
+        <v>0.4541651630699847</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>7.033232437325769E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.13031635139518519</v>
+        <v>0.07033233320964909</v>
       </c>
       <c r="D28">
-        <v>0.22709331144026851</v>
+        <v>0.1303162959565743</v>
       </c>
       <c r="E28">
-        <v>0.21242283323030331</v>
+        <v>0.2270933289727126</v>
       </c>
       <c r="F28">
-        <v>0.19835489902293191</v>
+        <v>0.2124227768885053</v>
       </c>
       <c r="G28">
-        <v>0.21490470575489229</v>
+        <v>0.1983548765087497</v>
       </c>
       <c r="H28">
-        <v>0.39318807337893258</v>
+        <v>0.2149047457634944</v>
       </c>
       <c r="I28">
-        <v>0.40650746117125158</v>
+        <v>0.3931880122245616</v>
       </c>
       <c r="J28">
-        <v>0.38950915037549388</v>
+        <v>0.4065074707586055</v>
       </c>
       <c r="K28">
-        <v>0.3423881567779814</v>
+        <v>0.3895091689396021</v>
       </c>
       <c r="L28">
-        <v>0.34143664879439428</v>
+        <v>0.3423881367801984</v>
       </c>
       <c r="M28">
-        <v>0.33378682830635159</v>
+        <v>0.3414366239119759</v>
       </c>
       <c r="N28">
-        <v>0.37532615922879192</v>
+        <v>0.3337867910393364</v>
       </c>
       <c r="O28">
-        <v>0.4107321841234659</v>
+        <v>0.3753261176913084</v>
       </c>
       <c r="P28">
-        <v>0.4422320511243103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.4107321517272675</v>
+      </c>
+      <c r="Q28">
+        <v>0.4422320052452592</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>7.1797607124829396E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.1380104689255936</v>
+        <v>0.07179763213584764</v>
       </c>
       <c r="D29">
-        <v>0.23439053507208191</v>
+        <v>0.1380104228963553</v>
       </c>
       <c r="E29">
-        <v>0.21711859018919191</v>
+        <v>0.2343905469727191</v>
       </c>
       <c r="F29">
-        <v>0.19911617700981529</v>
+        <v>0.2171184209444947</v>
       </c>
       <c r="G29">
-        <v>0.2092468717423312</v>
+        <v>0.1991160131422908</v>
       </c>
       <c r="H29">
-        <v>0.37838249780950761</v>
+        <v>0.209246878459963</v>
       </c>
       <c r="I29">
-        <v>0.37990235219684498</v>
+        <v>0.3783824256574394</v>
       </c>
       <c r="J29">
-        <v>0.37666304709716458</v>
+        <v>0.3799023506295949</v>
       </c>
       <c r="K29">
-        <v>0.32635755765560698</v>
+        <v>0.3766629940408113</v>
       </c>
       <c r="L29">
-        <v>0.32934781124847973</v>
+        <v>0.3263575402003367</v>
       </c>
       <c r="M29">
-        <v>0.31920747474341937</v>
+        <v>0.3293477888242468</v>
       </c>
       <c r="N29">
-        <v>0.36049740558159371</v>
+        <v>0.3192074436939009</v>
       </c>
       <c r="O29">
-        <v>0.38865014353513239</v>
+        <v>0.3604973723343898</v>
       </c>
       <c r="P29">
-        <v>0.41892612180061339</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.3886500938693868</v>
+      </c>
+      <c r="Q29">
+        <v>0.4189260768744967</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>7.2380327998954011E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.1357497423513036</v>
+        <v>0.07238034492941209</v>
       </c>
       <c r="D30">
-        <v>0.2296946078859842</v>
+        <v>0.1357496986580611</v>
       </c>
       <c r="E30">
-        <v>0.21461866331066129</v>
+        <v>0.2296946217200135</v>
       </c>
       <c r="F30">
-        <v>0.20466254056204081</v>
+        <v>0.2146186286284524</v>
       </c>
       <c r="G30">
-        <v>0.2170835832937128</v>
+        <v>0.2046625146299031</v>
       </c>
       <c r="H30">
-        <v>0.37749969081124918</v>
+        <v>0.2170835900104316</v>
       </c>
       <c r="I30">
-        <v>0.38731478846296991</v>
+        <v>0.3774996429994194</v>
       </c>
       <c r="J30">
-        <v>0.38524086177024208</v>
+        <v>0.3873147897025098</v>
       </c>
       <c r="K30">
-        <v>0.33500748131103741</v>
+        <v>0.3852408592784673</v>
       </c>
       <c r="L30">
-        <v>0.33685827208680807</v>
+        <v>0.3350074574587598</v>
       </c>
       <c r="M30">
-        <v>0.331023652137032</v>
+        <v>0.3368582465029533</v>
       </c>
       <c r="N30">
-        <v>0.36088262117421632</v>
+        <v>0.3310236027438249</v>
       </c>
       <c r="O30">
-        <v>0.38852897526944918</v>
+        <v>0.3608825794458638</v>
       </c>
       <c r="P30">
-        <v>0.40873248744891111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.3885289236349008</v>
+      </c>
+      <c r="Q30">
+        <v>0.4087324392560539</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>7.1669004092782498E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.12993085346946151</v>
+        <v>0.07166902880085817</v>
       </c>
       <c r="D31">
-        <v>0.22509123747601839</v>
+        <v>0.1299308016878895</v>
       </c>
       <c r="E31">
-        <v>0.20763816738525151</v>
+        <v>0.2250914603792901</v>
       </c>
       <c r="F31">
-        <v>0.19592352470001831</v>
+        <v>0.2076381176030721</v>
       </c>
       <c r="G31">
-        <v>0.20634234040097099</v>
+        <v>0.1959235209205527</v>
       </c>
       <c r="H31">
-        <v>0.36030682979941547</v>
+        <v>0.2063423485268039</v>
       </c>
       <c r="I31">
-        <v>0.36886355368831819</v>
+        <v>0.3603067676178966</v>
       </c>
       <c r="J31">
-        <v>0.3759897738284933</v>
+        <v>0.3688635379171477</v>
       </c>
       <c r="K31">
-        <v>0.33126021104118092</v>
+        <v>0.3759896986248026</v>
       </c>
       <c r="L31">
-        <v>0.33539349925446338</v>
+        <v>0.3312601858719262</v>
       </c>
       <c r="M31">
-        <v>0.32373569913025457</v>
+        <v>0.3353934797199805</v>
       </c>
       <c r="N31">
-        <v>0.35824051864360801</v>
+        <v>0.3237356579270348</v>
       </c>
       <c r="O31">
-        <v>0.38654923877356612</v>
+        <v>0.3582405247095158</v>
       </c>
       <c r="P31">
-        <v>0.39436345388370991</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.3865492149166894</v>
+      </c>
+      <c r="Q31">
+        <v>0.3943634445343882</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>6.9592287227978541E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.1359948597968211</v>
+        <v>0.06959229734225285</v>
       </c>
       <c r="D32">
-        <v>0.234096202147451</v>
+        <v>0.1359947828603028</v>
       </c>
       <c r="E32">
-        <v>0.22410110196885449</v>
+        <v>0.2340962370535578</v>
       </c>
       <c r="F32">
-        <v>0.20485296638564329</v>
+        <v>0.2241009824730636</v>
       </c>
       <c r="G32">
-        <v>0.22145278970289989</v>
+        <v>0.2048529070737052</v>
       </c>
       <c r="H32">
-        <v>0.42059361979999982</v>
+        <v>0.221452765867379</v>
       </c>
       <c r="I32">
-        <v>0.41165010380243461</v>
+        <v>0.4205935702193191</v>
       </c>
       <c r="J32">
-        <v>0.404621553562381</v>
+        <v>0.4116501095084928</v>
       </c>
       <c r="K32">
-        <v>0.37224462982160178</v>
+        <v>0.4046215495063928</v>
       </c>
       <c r="L32">
-        <v>0.36397707570719301</v>
+        <v>0.3722446086917942</v>
       </c>
       <c r="M32">
-        <v>0.36799779825861018</v>
+        <v>0.3639770491888277</v>
       </c>
       <c r="N32">
-        <v>0.41905717946323912</v>
+        <v>0.3679977613627666</v>
       </c>
       <c r="O32">
-        <v>0.47778378223119911</v>
+        <v>0.4190571148080064</v>
       </c>
       <c r="P32">
-        <v>0.53841167462800466</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.4777836981385116</v>
+      </c>
+      <c r="Q32">
+        <v>0.5384115570596999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>6.892750345540942E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.13073583441010239</v>
+        <v>0.06892751381657714</v>
       </c>
       <c r="D33">
-        <v>0.22743337470343539</v>
+        <v>0.1307357784666238</v>
       </c>
       <c r="E33">
-        <v>0.21129873992337311</v>
+        <v>0.2274333988053587</v>
       </c>
       <c r="F33">
-        <v>0.19638080852621109</v>
+        <v>0.2112986398231323</v>
       </c>
       <c r="G33">
-        <v>0.2118215306009055</v>
+        <v>0.196380737176008</v>
       </c>
       <c r="H33">
-        <v>0.40782081764493378</v>
+        <v>0.2118215314040642</v>
       </c>
       <c r="I33">
-        <v>0.39680275506378582</v>
+        <v>0.4078207880758282</v>
       </c>
       <c r="J33">
-        <v>0.38543495939471362</v>
+        <v>0.3968027598361414</v>
       </c>
       <c r="K33">
-        <v>0.35618517666836852</v>
+        <v>0.3854349980628117</v>
       </c>
       <c r="L33">
-        <v>0.35891555410673381</v>
+        <v>0.3561851588575819</v>
       </c>
       <c r="M33">
-        <v>0.35594449778830223</v>
+        <v>0.3589155371688936</v>
       </c>
       <c r="N33">
-        <v>0.39965661479020059</v>
+        <v>0.355944463292283</v>
       </c>
       <c r="O33">
-        <v>0.44609589273621469</v>
+        <v>0.3996565851001153</v>
       </c>
       <c r="P33">
-        <v>0.49948336726140508</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.4460958453362159</v>
+      </c>
+      <c r="Q33">
+        <v>0.4994832902442541</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>6.8050493819678454E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.13392518109946719</v>
+        <v>0.06805050511669337</v>
       </c>
       <c r="D34">
-        <v>0.23113633884070869</v>
+        <v>0.1339251277778058</v>
       </c>
       <c r="E34">
-        <v>0.22166198745419199</v>
+        <v>0.231136360007791</v>
       </c>
       <c r="F34">
-        <v>0.2042490869382669</v>
+        <v>0.2216618980181379</v>
       </c>
       <c r="G34">
-        <v>0.21873593215916889</v>
+        <v>0.2042490558828725</v>
       </c>
       <c r="H34">
-        <v>0.39693227416610172</v>
+        <v>0.2187359398559722</v>
       </c>
       <c r="I34">
-        <v>0.40531035612580979</v>
+        <v>0.3969322234657214</v>
       </c>
       <c r="J34">
-        <v>0.39271779473659812</v>
+        <v>0.4053103547235716</v>
       </c>
       <c r="K34">
-        <v>0.36570205585041288</v>
+        <v>0.3927177922790006</v>
       </c>
       <c r="L34">
-        <v>0.35762055110958002</v>
+        <v>0.3657020269583044</v>
       </c>
       <c r="M34">
-        <v>0.35622518440039658</v>
+        <v>0.3576205214456823</v>
       </c>
       <c r="N34">
-        <v>0.39310103841697158</v>
+        <v>0.3562251474804652</v>
       </c>
       <c r="O34">
-        <v>0.43714002915102868</v>
+        <v>0.3931009902885326</v>
       </c>
       <c r="P34">
-        <v>0.48397531838110808</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.4371399667608834</v>
+      </c>
+      <c r="Q34">
+        <v>0.4839752664571768</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>7.3909585976651856E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.14420920715682631</v>
+        <v>0.07390960564562583</v>
       </c>
       <c r="D35">
-        <v>0.23815787371139399</v>
+        <v>0.1442091526597566</v>
       </c>
       <c r="E35">
-        <v>0.22431510166363411</v>
+        <v>0.2381579004070277</v>
       </c>
       <c r="F35">
-        <v>0.21026381638982289</v>
+        <v>0.2243150283548443</v>
       </c>
       <c r="G35">
-        <v>0.22702093900152609</v>
+        <v>0.2102638041515464</v>
       </c>
       <c r="H35">
-        <v>0.40404650892937671</v>
+        <v>0.2270209467674388</v>
       </c>
       <c r="I35">
-        <v>0.40581316901291248</v>
+        <v>0.404046454401033</v>
       </c>
       <c r="J35">
-        <v>0.39353032955703321</v>
+        <v>0.4058131763681547</v>
       </c>
       <c r="K35">
-        <v>0.36479577878372299</v>
+        <v>0.3935303117712958</v>
       </c>
       <c r="L35">
-        <v>0.36953368588604302</v>
+        <v>0.3647957573679895</v>
       </c>
       <c r="M35">
-        <v>0.35825846282516161</v>
+        <v>0.3695336570366281</v>
       </c>
       <c r="N35">
-        <v>0.38729765832366719</v>
+        <v>0.3582584322342164</v>
       </c>
       <c r="O35">
-        <v>0.42593425945790953</v>
+        <v>0.3872976194134621</v>
       </c>
       <c r="P35">
-        <v>0.46083810665293862</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.4259342176362685</v>
+      </c>
+      <c r="Q35">
+        <v>0.4608380612562529</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>6.8461718169891675E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.13580317594275501</v>
+        <v>0.06846173214754382</v>
       </c>
       <c r="D36">
-        <v>0.22925581298229131</v>
+        <v>0.1358031302724149</v>
       </c>
       <c r="E36">
-        <v>0.208797231582007</v>
+        <v>0.2292558393380052</v>
       </c>
       <c r="F36">
-        <v>0.19734356135418801</v>
+        <v>0.2087971806539371</v>
       </c>
       <c r="G36">
-        <v>0.21024453811745089</v>
+        <v>0.1973434989371686</v>
       </c>
       <c r="H36">
-        <v>0.34166372034355069</v>
+        <v>0.210244503827941</v>
       </c>
       <c r="I36">
-        <v>0.35891410005160951</v>
+        <v>0.3416636745628964</v>
       </c>
       <c r="J36">
-        <v>0.35800116867047421</v>
+        <v>0.3589141045443705</v>
       </c>
       <c r="K36">
-        <v>0.3293115121510316</v>
+        <v>0.3580011656445837</v>
       </c>
       <c r="L36">
-        <v>0.3309908040046432</v>
+        <v>0.3293114886338528</v>
       </c>
       <c r="M36">
-        <v>0.32516086531930261</v>
+        <v>0.3309907745727484</v>
       </c>
       <c r="N36">
-        <v>0.35014238392506358</v>
+        <v>0.3251608291162462</v>
       </c>
       <c r="O36">
-        <v>0.3898122213154499</v>
+        <v>0.3501423446893923</v>
       </c>
       <c r="P36">
-        <v>0.40188123165053319</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.3898121823000352</v>
+      </c>
+      <c r="Q36">
+        <v>0.4018811874025792</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.14946199681296191</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.33662921590394418</v>
+        <v>0.1494618092590716</v>
       </c>
       <c r="D37">
-        <v>0.29183434634435901</v>
+        <v>0.3366291378935644</v>
       </c>
       <c r="E37">
-        <v>0.32082983152628147</v>
+        <v>0.2918343381958962</v>
       </c>
       <c r="F37">
-        <v>0.51964287399558406</v>
+        <v>0.3208298936717507</v>
       </c>
       <c r="G37">
-        <v>0.54707954475308473</v>
+        <v>0.5196429372637128</v>
       </c>
       <c r="H37">
-        <v>0.55715198824854428</v>
+        <v>0.5470796223236787</v>
       </c>
       <c r="I37">
-        <v>0.5559870997584947</v>
+        <v>0.557151936874233</v>
       </c>
       <c r="J37">
-        <v>0.59960778084734712</v>
+        <v>0.5559869799083617</v>
       </c>
       <c r="K37">
-        <v>0.65547059807049024</v>
+        <v>0.5996076710090285</v>
       </c>
       <c r="L37">
-        <v>0.707829785725274</v>
+        <v>0.6554704625234377</v>
       </c>
       <c r="M37">
-        <v>0.77809099688523264</v>
+        <v>0.7078296053457358</v>
       </c>
       <c r="N37">
-        <v>0.78046875177824038</v>
+        <v>0.7780907967261911</v>
       </c>
       <c r="O37">
-        <v>0.79495019060900041</v>
+        <v>0.780468403269904</v>
       </c>
       <c r="P37">
-        <v>0.80253196754516765</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.7949496020329432</v>
+      </c>
+      <c r="Q37">
+        <v>0.8025311366725809</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>9.9967437938747516E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.2484942007802167</v>
+        <v>0.09996737344289468</v>
       </c>
       <c r="D38">
-        <v>0.25232743601790297</v>
+        <v>0.2484941725337643</v>
       </c>
       <c r="E38">
-        <v>0.29374815726366288</v>
+        <v>0.2523276666878008</v>
       </c>
       <c r="F38">
-        <v>0.47536304899512222</v>
+        <v>0.2937481436569672</v>
       </c>
       <c r="G38">
-        <v>0.36723805549985661</v>
+        <v>0.4753631044688529</v>
       </c>
       <c r="H38">
-        <v>0.27185677180853279</v>
+        <v>0.3672381069382668</v>
       </c>
       <c r="I38">
-        <v>0.33173692902979829</v>
+        <v>0.2718567562173584</v>
       </c>
       <c r="J38">
-        <v>0.4056714459868237</v>
+        <v>0.3317374876458923</v>
       </c>
       <c r="K38">
-        <v>0.47809836823846508</v>
+        <v>0.4056714147648054</v>
       </c>
       <c r="L38">
-        <v>0.52325285876053373</v>
+        <v>0.47809827883861</v>
       </c>
       <c r="M38">
-        <v>0.57142467459002455</v>
+        <v>0.523252755818209</v>
       </c>
       <c r="N38">
-        <v>0.61444380368401885</v>
+        <v>0.5714245660914546</v>
       </c>
       <c r="O38">
-        <v>0.6364221033296299</v>
+        <v>0.6144437602576196</v>
       </c>
       <c r="P38">
-        <v>0.64558818999748002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.6364219930191544</v>
+      </c>
+      <c r="Q38">
+        <v>0.6455880028969818</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>9.5777054104029882E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.22252128298762169</v>
+        <v>0.09577697473214501</v>
       </c>
       <c r="D39">
-        <v>0.2193885566570225</v>
+        <v>0.222521228013197</v>
       </c>
       <c r="E39">
-        <v>0.2154762422409148</v>
+        <v>0.2193887130451424</v>
       </c>
       <c r="F39">
-        <v>0.33544217097186402</v>
+        <v>0.2154761503807837</v>
       </c>
       <c r="G39">
-        <v>0.27323018608714739</v>
+        <v>0.3354420667584421</v>
       </c>
       <c r="H39">
-        <v>0.25962991359225479</v>
+        <v>0.2732301949118697</v>
       </c>
       <c r="I39">
-        <v>0.30752422669915391</v>
+        <v>0.25962995948815</v>
       </c>
       <c r="J39">
-        <v>0.35341422243073328</v>
+        <v>0.3075242868125106</v>
       </c>
       <c r="K39">
-        <v>0.38806264757737718</v>
+        <v>0.3534141416865512</v>
       </c>
       <c r="L39">
-        <v>0.44208109468587198</v>
+        <v>0.38806260364849</v>
       </c>
       <c r="M39">
-        <v>0.4510486974179197</v>
+        <v>0.442081004540633</v>
       </c>
       <c r="N39">
-        <v>0.51073198384810259</v>
+        <v>0.4510485944178002</v>
       </c>
       <c r="O39">
-        <v>0.5564577433233393</v>
+        <v>0.5107318703380058</v>
       </c>
       <c r="P39">
-        <v>0.59112789448577308</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.5564575812548211</v>
+      </c>
+      <c r="Q39">
+        <v>0.5911276761247063</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.1429144158603998</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.13457284710328929</v>
+        <v>0.142914366336394</v>
       </c>
       <c r="D40">
-        <v>0.20601855466311339</v>
+        <v>0.1345728140370359</v>
       </c>
       <c r="E40">
-        <v>0.27463672658901522</v>
+        <v>0.2060185609241602</v>
       </c>
       <c r="F40">
-        <v>0.37178756585934009</v>
+        <v>0.2746367584645566</v>
       </c>
       <c r="G40">
-        <v>0.37710369130849808</v>
+        <v>0.3717875732777609</v>
       </c>
       <c r="H40">
-        <v>0.44889819091072919</v>
+        <v>0.3771036949132562</v>
       </c>
       <c r="I40">
-        <v>0.54890570607273825</v>
+        <v>0.4488981649795818</v>
       </c>
       <c r="J40">
-        <v>0.61378312193818096</v>
+        <v>0.5489055858230043</v>
       </c>
       <c r="K40">
-        <v>0.62797781283787601</v>
+        <v>0.6137829521396868</v>
       </c>
       <c r="L40">
-        <v>0.65482470785099767</v>
+        <v>0.6279776501674628</v>
       </c>
       <c r="M40">
-        <v>0.65534098582094669</v>
+        <v>0.6548245540114987</v>
       </c>
       <c r="N40">
-        <v>0.69344180644365871</v>
+        <v>0.6553407962626283</v>
       </c>
       <c r="O40">
-        <v>0.74159895841984314</v>
+        <v>0.6934414318004665</v>
       </c>
       <c r="P40">
-        <v>0.82294851348201747</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.741598436898897</v>
+      </c>
+      <c r="Q40">
+        <v>0.8229477640852977</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.1771686227038399</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.50058384585817062</v>
+        <v>0.1771686816349197</v>
       </c>
       <c r="D41">
-        <v>0.49952058248617659</v>
+        <v>0.5005838298126755</v>
       </c>
       <c r="E41">
-        <v>0.58676013824674755</v>
+        <v>0.4995205570577253</v>
       </c>
       <c r="F41">
-        <v>0.62212103675732466</v>
+        <v>0.5867601431292085</v>
       </c>
       <c r="G41">
-        <v>0.65150309886198177</v>
+        <v>0.6221210582485146</v>
       </c>
       <c r="H41">
-        <v>0.69282473757271179</v>
+        <v>0.6515030948213398</v>
       </c>
       <c r="I41">
-        <v>0.69316023661045978</v>
+        <v>0.6928247359038322</v>
       </c>
       <c r="J41">
-        <v>0.75619773748434715</v>
+        <v>0.6931602410557087</v>
       </c>
       <c r="K41">
-        <v>0.82453418725004601</v>
+        <v>0.7561977779659307</v>
       </c>
       <c r="L41">
-        <v>0.84871416536482081</v>
+        <v>0.8245340676207387</v>
       </c>
       <c r="M41">
-        <v>0.91196377866532363</v>
+        <v>0.8487140508807127</v>
       </c>
       <c r="N41">
-        <v>0.99710884997736793</v>
+        <v>0.9119635632786877</v>
       </c>
       <c r="O41">
-        <v>1.027946226212533</v>
+        <v>0.9971086028051374</v>
       </c>
       <c r="P41">
-        <v>1.064364337808434</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>1.027945966139124</v>
+      </c>
+      <c r="Q41">
+        <v>1.064364034533541</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>6.130306461208046E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.61854879760624759</v>
+        <v>0.06130306712928991</v>
       </c>
       <c r="D42">
-        <v>0.54910856301852984</v>
+        <v>0.6185489962349284</v>
       </c>
       <c r="E42">
-        <v>0.43017186652730199</v>
+        <v>0.549108876666746</v>
       </c>
       <c r="F42">
-        <v>0.41806648598825003</v>
+        <v>0.430171926567363</v>
       </c>
       <c r="G42">
-        <v>0.45259408454769962</v>
+        <v>0.418066520475541</v>
       </c>
       <c r="H42">
-        <v>0.42710028418750118</v>
+        <v>0.4525940381904056</v>
       </c>
       <c r="I42">
-        <v>0.45035823452942508</v>
+        <v>0.4271002962583699</v>
       </c>
       <c r="J42">
-        <v>0.50319324736793858</v>
+        <v>0.4503582177390014</v>
       </c>
       <c r="K42">
-        <v>0.51768070053990289</v>
+        <v>0.5031932413085729</v>
       </c>
       <c r="L42">
-        <v>0.54622328621411775</v>
+        <v>0.5176806196780437</v>
       </c>
       <c r="M42">
-        <v>0.61167091962006559</v>
+        <v>0.5462232243523847</v>
       </c>
       <c r="N42">
-        <v>0.64388741408078443</v>
+        <v>0.61167081416087</v>
       </c>
       <c r="O42">
-        <v>0.65642310222002154</v>
+        <v>0.6438872764700018</v>
       </c>
       <c r="P42">
-        <v>0.69377526467761508</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.6564229178901791</v>
+      </c>
+      <c r="Q42">
+        <v>0.6937750484968869</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>9.8092565479863933E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.23751057504353101</v>
+        <v>0.09809261894487618</v>
       </c>
       <c r="D43">
-        <v>0.38490958568749201</v>
+        <v>0.2375105798048512</v>
       </c>
       <c r="E43">
-        <v>0.45397972553260241</v>
+        <v>0.3849096829287435</v>
       </c>
       <c r="F43">
-        <v>0.36106889953267568</v>
+        <v>0.4539797463786893</v>
       </c>
       <c r="G43">
-        <v>0.36548058242166781</v>
+        <v>0.3610688944507511</v>
       </c>
       <c r="H43">
-        <v>0.40452797802305979</v>
+        <v>0.3654806600120498</v>
       </c>
       <c r="I43">
-        <v>0.45981669045018198</v>
+        <v>0.4045279985899248</v>
       </c>
       <c r="J43">
-        <v>0.56076189866103587</v>
+        <v>0.459816699422397</v>
       </c>
       <c r="K43">
-        <v>0.55652535222060817</v>
+        <v>0.5607618831335991</v>
       </c>
       <c r="L43">
-        <v>0.57796767468150723</v>
+        <v>0.5565253356090071</v>
       </c>
       <c r="M43">
-        <v>0.59936167275839947</v>
+        <v>0.5779676900849049</v>
       </c>
       <c r="N43">
-        <v>0.64227493550983283</v>
+        <v>0.5993615131397221</v>
       </c>
       <c r="O43">
-        <v>0.67818689146705669</v>
+        <v>0.6422751457059833</v>
       </c>
       <c r="P43">
-        <v>0.70857553279714702</v>
+        <v>0.6781871075323237</v>
+      </c>
+      <c r="Q43">
+        <v>0.7085754123254535</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P43">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>